--- a/BRO.xlsx
+++ b/BRO.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H673"/>
+  <dimension ref="A1:H687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21335,7 +21335,7 @@
         <v>1.833333333333333</v>
       </c>
       <c r="D633" s="2" t="n">
-        <v>1.878472222222222</v>
+        <v>1.867764641967593</v>
       </c>
       <c r="E633" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -22450,30 +22450,30 @@
         </is>
       </c>
       <c r="C667" s="2" t="n">
-        <v>1.756597222222222</v>
+        <v>1.799305555555556</v>
       </c>
       <c r="D667" s="2" t="n">
-        <v>1.759375</v>
+        <v>1.823304512337963</v>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>material trip</t>
+          <t>charging</t>
         </is>
       </c>
       <c r="F667" t="inlineStr"/>
       <c r="G667" t="n">
-        <v>1.979999999999999</v>
+        <v>-93.43873333333335</v>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -22482,30 +22482,30 @@
         </is>
       </c>
       <c r="C668" s="2" t="n">
-        <v>1.804861111111111</v>
+        <v>1.840972222222222</v>
       </c>
       <c r="D668" s="2" t="n">
-        <v>1.807638888888889</v>
+        <v>1.865397845671296</v>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>material trip</t>
+          <t>charging</t>
         </is>
       </c>
       <c r="F668" t="inlineStr"/>
       <c r="G668" t="n">
-        <v>1.979999999999999</v>
+        <v>-98.04673333333335</v>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -22514,23 +22514,23 @@
         </is>
       </c>
       <c r="C669" s="2" t="n">
-        <v>1.735763888888889</v>
+        <v>1.840972222222222</v>
       </c>
       <c r="D669" s="2" t="n">
-        <v>1.738541666666667</v>
+        <v>1.863322851840278</v>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>material trip</t>
+          <t>charging</t>
         </is>
       </c>
       <c r="F669" t="inlineStr"/>
       <c r="G669" t="n">
-        <v>1.979999999999999</v>
+        <v>-75.63679999999999</v>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -22546,10 +22546,10 @@
         </is>
       </c>
       <c r="C670" s="2" t="n">
-        <v>1.840972222222222</v>
+        <v>1.756597222222222</v>
       </c>
       <c r="D670" s="2" t="n">
-        <v>1.84375</v>
+        <v>1.759375</v>
       </c>
       <c r="E670" t="inlineStr">
         <is>
@@ -22562,14 +22562,14 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -22578,30 +22578,30 @@
         </is>
       </c>
       <c r="C671" s="2" t="n">
-        <v>2.037847222222222</v>
+        <v>1.759375</v>
       </c>
       <c r="D671" s="2" t="n">
-        <v>2.040625</v>
+        <v>1.789916722222222</v>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>material trip</t>
+          <t>charging</t>
         </is>
       </c>
       <c r="F671" t="inlineStr"/>
       <c r="G671" t="n">
-        <v>1.979999999999999</v>
+        <v>-164.1006</v>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -22610,30 +22610,30 @@
         </is>
       </c>
       <c r="C672" s="2" t="n">
-        <v>2.017013888888889</v>
+        <v>1.878472222222222</v>
       </c>
       <c r="D672" s="2" t="n">
-        <v>2.019791666666667</v>
+        <v>1.894875660486111</v>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>material trip</t>
+          <t>charging</t>
         </is>
       </c>
       <c r="F672" t="inlineStr"/>
       <c r="G672" t="n">
-        <v>1.979999999999999</v>
+        <v>-23.62095111111108</v>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>bus14</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -22642,21 +22642,469 @@
         </is>
       </c>
       <c r="C673" s="2" t="n">
-        <v>2.022222222222222</v>
+        <v>1.69375</v>
       </c>
       <c r="D673" s="2" t="n">
-        <v>2.036111111111111</v>
+        <v>1.71864744443287</v>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>material trip</t>
+          <t>charging</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
       <c r="G673" t="n">
+        <v>-103.1423999999999</v>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>bus7</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="C674" s="2" t="n">
+        <v>1.804861111111111</v>
+      </c>
+      <c r="D674" s="2" t="n">
+        <v>1.807638888888889</v>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr"/>
+      <c r="G674" t="n">
+        <v>1.979999999999999</v>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>bus8</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="C675" s="2" t="n">
+        <v>1.807638888888889</v>
+      </c>
+      <c r="D675" s="2" t="n">
+        <v>1.837612580243055</v>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr"/>
+      <c r="G675" t="n">
+        <v>-157.9658666666666</v>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>bus8</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="C676" s="2" t="n">
+        <v>1.735763888888889</v>
+      </c>
+      <c r="D676" s="2" t="n">
+        <v>1.738541666666667</v>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr"/>
+      <c r="G676" t="n">
+        <v>1.979999999999999</v>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>bus9</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="C677" s="2" t="n">
+        <v>1.738541666666667</v>
+      </c>
+      <c r="D677" s="2" t="n">
+        <v>1.766544012337963</v>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr"/>
+      <c r="G677" t="n">
+        <v>-136.6753333333334</v>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>bus9</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="C678" s="2" t="n">
+        <v>1.840972222222222</v>
+      </c>
+      <c r="D678" s="2" t="n">
+        <v>1.84375</v>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr"/>
+      <c r="G678" t="n">
+        <v>1.979999999999999</v>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>bus10</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="C679" s="2" t="n">
+        <v>1.84375</v>
+      </c>
+      <c r="D679" s="2" t="n">
+        <v>1.875986253078704</v>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr"/>
+      <c r="G679" t="n">
+        <v>-182.4015333333334</v>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>bus10</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="C680" s="2" t="n">
+        <v>1.714583333333333</v>
+      </c>
+      <c r="D680" s="2" t="n">
+        <v>1.739689388888889</v>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr"/>
+      <c r="G680" t="n">
+        <v>-105.3954</v>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>bus11</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="C681" s="2" t="n">
+        <v>1.735416666666667</v>
+      </c>
+      <c r="D681" s="2" t="n">
+        <v>1.760368802465278</v>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr"/>
+      <c r="G681" t="n">
+        <v>-103.7330666666667</v>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>bus12</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="C682" s="2" t="n">
+        <v>2.037847222222222</v>
+      </c>
+      <c r="D682" s="2" t="n">
+        <v>2.040625</v>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr"/>
+      <c r="G682" t="n">
+        <v>1.979999999999999</v>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>bus13</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="C683" s="2" t="n">
+        <v>2.040625</v>
+      </c>
+      <c r="D683" s="2" t="n">
+        <v>2.060145074895833</v>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr"/>
+      <c r="G683" t="n">
+        <v>-45.06680888888891</v>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>bus13</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="C684" s="2" t="n">
+        <v>2.017013888888889</v>
+      </c>
+      <c r="D684" s="2" t="n">
+        <v>2.019791666666667</v>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr"/>
+      <c r="G684" t="n">
+        <v>1.979999999999999</v>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>bus14</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="C685" s="2" t="n">
+        <v>2.019791666666667</v>
+      </c>
+      <c r="D685" s="2" t="n">
+        <v>2.054981734560185</v>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr"/>
+      <c r="G685" t="n">
+        <v>-214.3027333333334</v>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>bus14</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="C686" s="2" t="n">
+        <v>2.022222222222222</v>
+      </c>
+      <c r="D686" s="2" t="n">
+        <v>2.036111111111111</v>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr"/>
+      <c r="G686" t="n">
         <v>10.8</v>
       </c>
-      <c r="H673" t="inlineStr">
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>bus15</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="C687" s="2" t="n">
+        <v>2.036111111111111</v>
+      </c>
+      <c r="D687" s="2" t="n">
+        <v>2.067901222222222</v>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr"/>
+      <c r="G687" t="n">
+        <v>-177.5832</v>
+      </c>
+      <c r="H687" t="inlineStr">
         <is>
           <t>bus15</t>
         </is>
